--- a/data/trans_orig/P15B_3_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P15B_3_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2007</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2007 (tasa de respuesta: 51,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>920</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>880</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>13473</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19441</t>
+          <t>19478</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -1076,97 +1076,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1792</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1884</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11489</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13281</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16984</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>14441</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23694</t>
+          <t>24018</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13849</t>
+          <t>13772</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25320</t>
+          <t>25186</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>75,76%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>13844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>19470</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,57%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19117</t>
+          <t>18717</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12953</t>
+          <t>12665</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>13453</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29656</t>
+          <t>28720</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20306</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31491</t>
+          <t>32009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21541</t>
+          <t>21622</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34376</t>
+          <t>35312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50115</t>
+          <t>50579</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,99%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11388</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>11548</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23702</t>
+          <t>22988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33029</t>
+          <t>32940</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -2448,97 +2448,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1908</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26134</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28042</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42313</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44234</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29153</t>
+          <t>30165</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50071</t>
+          <t>51177</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17783</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37046</t>
+          <t>37690</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62814</t>
+          <t>61689</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>71949</t>
+          <t>70843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92867</t>
+          <t>91855</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>76023</t>
+          <t>76731</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>88843</t>
+          <t>89103</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>153011</t>
+          <t>154136</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>178779</t>
+          <t>178135</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,54%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2012</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2012 (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9379</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15155</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24989</t>
+          <t>24943</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33007</t>
+          <t>33001</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36136</t>
+          <t>35910</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48272</t>
+          <t>48160</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>911</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>20899</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30582</t>
+          <t>30572</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25832</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47434</t>
+          <t>47253</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56418</t>
+          <t>56426</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22028</t>
+          <t>21243</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21381</t>
+          <t>21829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37769</t>
+          <t>38554</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51246</t>
+          <t>51963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15013</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53429</t>
+          <t>52981</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66886</t>
+          <t>66781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,27%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17170</t>
+          <t>15883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32444</t>
+          <t>32183</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12150</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22076</t>
+          <t>21065</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40376</t>
+          <t>41195</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63176</t>
+          <t>63437</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78450</t>
+          <t>79737</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36529</t>
+          <t>36954</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46557</t>
+          <t>46496</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>103923</t>
+          <t>103104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122223</t>
+          <t>123234</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>85,4%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9542</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22094</t>
+          <t>22844</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11441</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28152</t>
+          <t>28288</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17169</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29721</t>
+          <t>28841</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50635</t>
+          <t>51556</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69337</t>
+          <t>69201</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86052</t>
+          <t>86048</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,26%</t>
         </is>
       </c>
     </row>
@@ -5083,97 +5083,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1183</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1763</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6627</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1183</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4774</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5935</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4972</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25062</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26825</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>85551</t>
+          <t>83698</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112178</t>
+          <t>111215</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>48742</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77841</t>
+          <t>76648</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23649</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60244</t>
+          <t>59450</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94567</t>
+          <t>94118</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>209131</t>
+          <t>210324</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>237476</t>
+          <t>238230</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>231756</t>
+          <t>232272</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>248464</t>
+          <t>248844</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>447810</t>
+          <t>448259</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>482133</t>
+          <t>482927</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2016</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2016 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>988</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15355</t>
+          <t>15599</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>11942</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19160</t>
+          <t>19082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30328</t>
+          <t>30625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39600</t>
+          <t>39654</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>929</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10954</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16364</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30748</t>
+          <t>30992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37995</t>
+          <t>38017</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>15443</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>16092</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15294</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26252</t>
+          <t>26967</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25064</t>
+          <t>24961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36741</t>
+          <t>36338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>16583</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>8041</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21279</t>
+          <t>21269</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42130</t>
+          <t>42409</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53955</t>
+          <t>53202</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29445</t>
+          <t>30090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37497</t>
+          <t>37492</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76178</t>
+          <t>76188</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89653</t>
+          <t>89416</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12453</t>
+          <t>12382</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20281</t>
+          <t>20007</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28324</t>
+          <t>28395</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37902</t>
+          <t>37995</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29977</t>
+          <t>28755</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38352</t>
+          <t>38302</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60907</t>
+          <t>61181</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74828</t>
+          <t>74945</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -7718,97 +7718,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2181</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26525</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28538</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58254</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86816</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88973</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>20451</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>40329</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22882</t>
+          <t>21957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31716</t>
+          <t>31690</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56626</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>157265</t>
+          <t>157440</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>177556</t>
+          <t>177318</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>168571</t>
+          <t>169496</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>183307</t>
+          <t>183533</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>332597</t>
+          <t>331998</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>357507</t>
+          <t>357533</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2023</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>8756</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15312</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20092</t>
+          <t>19967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37063</t>
+          <t>38289</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46387</t>
+          <t>46389</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>855</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17573</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18344</t>
+          <t>18638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39388</t>
+          <t>39494</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46492</t>
+          <t>46451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>13557</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14571</t>
+          <t>15292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>34,43%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>18854</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28734</t>
+          <t>28152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29838</t>
+          <t>29117</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40230</t>
+          <t>40024</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26314</t>
+          <t>25682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16826</t>
+          <t>16233</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35639</t>
+          <t>34170</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40175</t>
+          <t>40807</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55821</t>
+          <t>55680</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35660</t>
+          <t>36638</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46613</t>
+          <t>46576</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80354</t>
+          <t>81823</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99167</t>
+          <t>99760</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24047</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11010</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13879</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34670</t>
+          <t>31232</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14261</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29456</t>
+          <t>29275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42115</t>
+          <t>42430</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49645</t>
+          <t>49760</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56764</t>
+          <t>60202</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77555</t>
+          <t>78131</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,45%</t>
         </is>
       </c>
     </row>
@@ -10353,97 +10353,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3098</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1160</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1347</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45481</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46641</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58370</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34759</t>
+          <t>34408</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62641</t>
+          <t>62141</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>10189</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23560</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47056</t>
+          <t>48091</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77360</t>
+          <t>78353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>134280</t>
+          <t>134780</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>162162</t>
+          <t>162513</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>184076</t>
+          <t>183107</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>197816</t>
+          <t>197447</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>327198</t>
+          <t>326205</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>357502</t>
+          <t>356467</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15B_3_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P15B_3_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11678</t>
+          <t>11681</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19478</t>
+          <t>19447</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>24073</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13772</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25186</t>
+          <t>25107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>13964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19470</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,52%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18717</t>
+          <t>18355</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12665</t>
+          <t>12652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13453</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28720</t>
+          <t>28693</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20306</t>
+          <t>20668</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32009</t>
+          <t>31438</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>12358</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>21162</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35312</t>
+          <t>35339</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50579</t>
+          <t>50140</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8457</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11548</t>
+          <t>11640</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15517</t>
+          <t>16592</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22988</t>
+          <t>22876</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32940</t>
+          <t>33095</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30165</t>
+          <t>28923</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51177</t>
+          <t>50647</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37690</t>
+          <t>36733</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61689</t>
+          <t>61658</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>70843</t>
+          <t>71373</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>91855</t>
+          <t>93097</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>76731</t>
+          <t>76808</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>89103</t>
+          <t>89342</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>154136</t>
+          <t>154167</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>178135</t>
+          <t>179092</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,98%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15381</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24943</t>
+          <t>24605</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33001</t>
+          <t>33018</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35910</t>
+          <t>36078</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48160</t>
+          <t>48370</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>920</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>924</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>12095</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20899</t>
+          <t>20699</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30572</t>
+          <t>30585</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47253</t>
+          <t>45242</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56426</t>
+          <t>56413</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7794</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21243</t>
+          <t>21007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21829</t>
+          <t>21391</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38554</t>
+          <t>38790</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51963</t>
+          <t>52003</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52981</t>
+          <t>53419</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66781</t>
+          <t>66510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,91%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15883</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32183</t>
+          <t>33058</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>12384</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21065</t>
+          <t>21974</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41195</t>
+          <t>40750</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63437</t>
+          <t>62562</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79737</t>
+          <t>79413</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36954</t>
+          <t>36295</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46496</t>
+          <t>45757</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>103104</t>
+          <t>103549</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123234</t>
+          <t>122325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>84,77%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10422</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22844</t>
+          <t>22684</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11441</t>
+          <t>11537</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28288</t>
+          <t>27970</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16419</t>
+          <t>16579</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28841</t>
+          <t>29081</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51556</t>
+          <t>50542</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69201</t>
+          <t>69519</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86048</t>
+          <t>85952</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83698</t>
+          <t>84426</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111215</t>
+          <t>111006</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48742</t>
+          <t>48908</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76648</t>
+          <t>76630</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>23025</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59450</t>
+          <t>60449</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94118</t>
+          <t>92848</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>210324</t>
+          <t>210342</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>238230</t>
+          <t>238064</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>232272</t>
+          <t>232380</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>248844</t>
+          <t>248400</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>448259</t>
+          <t>449529</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>482927</t>
+          <t>481928</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>904</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11942</t>
+          <t>12119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19082</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30625</t>
+          <t>30586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39654</t>
+          <t>39519</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>933</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>17040</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30992</t>
+          <t>31428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38017</t>
+          <t>38013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15443</t>
+          <t>15011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15624</t>
+          <t>16056</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26967</t>
+          <t>26721</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24961</t>
+          <t>25716</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36338</t>
+          <t>36659</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16583</t>
+          <t>16964</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8041</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21269</t>
+          <t>21177</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42409</t>
+          <t>42028</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53202</t>
+          <t>53996</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30090</t>
+          <t>29452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37492</t>
+          <t>37454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76188</t>
+          <t>76280</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89416</t>
+          <t>89597</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>13312</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11656</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6840</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20007</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28395</t>
+          <t>27465</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37995</t>
+          <t>37887</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28755</t>
+          <t>29549</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38302</t>
+          <t>38342</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61181</t>
+          <t>61865</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74945</t>
+          <t>74348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20451</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40329</t>
+          <t>40235</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21957</t>
+          <t>22800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31690</t>
+          <t>32791</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57225</t>
+          <t>58691</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>157440</t>
+          <t>157534</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>177318</t>
+          <t>177725</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>169496</t>
+          <t>168653</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>183533</t>
+          <t>183351</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>331998</t>
+          <t>330532</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>357533</t>
+          <t>356432</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8229</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>724</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>742</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -8746,27 +8746,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21043</t>
+          <t>22859</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15607</t>
+          <t>16801</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23836</t>
+          <t>25867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8781,27 +8781,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22572</t>
+          <t>25464</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19967</t>
+          <t>22460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23209</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>43615</t>
+          <t>48325</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38289</t>
+          <t>42210</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46389</t>
+          <t>51314</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23836</t>
+          <t>25867</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23836</t>
+          <t>25867</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23836</t>
+          <t>25867</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23209</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23209</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23209</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>47045</t>
+          <t>52056</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47045</t>
+          <t>52056</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47045</t>
+          <t>52056</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>9276</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -9089,27 +9089,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22149</t>
+          <t>23557</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17769</t>
+          <t>18849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24147</t>
+          <t>25732</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9124,27 +9124,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21742</t>
+          <t>23534</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18638</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>43891</t>
+          <t>47090</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39494</t>
+          <t>41438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46451</t>
+          <t>49509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24147</t>
+          <t>25732</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24147</t>
+          <t>25732</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24147</t>
+          <t>25732</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>47306</t>
+          <t>50714</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47306</t>
+          <t>50714</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>47306</t>
+          <t>50714</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>15321</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>544</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15292</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24178</t>
+          <t>27220</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18854</t>
+          <t>20838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28152</t>
+          <t>31462</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,27 +9467,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11456</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>35634</t>
+          <t>39365</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29117</t>
+          <t>32744</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40024</t>
+          <t>43985</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32411</t>
+          <t>36159</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32411</t>
+          <t>36159</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32411</t>
+          <t>36159</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>44409</t>
+          <t>48848</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44409</t>
+          <t>48848</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44409</t>
+          <t>48848</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18005</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10809</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25682</t>
+          <t>28923</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12866</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>24818</t>
+          <t>27004</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16233</t>
+          <t>17821</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34170</t>
+          <t>38034</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>48484</t>
+          <t>58021</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40807</t>
+          <t>48857</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55680</t>
+          <t>65729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>42691</t>
+          <t>48149</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36638</t>
+          <t>41060</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46576</t>
+          <t>52153</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>91175</t>
+          <t>106170</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81823</t>
+          <t>95140</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99760</t>
+          <t>115353</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,62%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66489</t>
+          <t>77780</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66489</t>
+          <t>77780</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66489</t>
+          <t>77780</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49504</t>
+          <t>55394</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49504</t>
+          <t>55394</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49504</t>
+          <t>55394</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>115993</t>
+          <t>133174</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>115993</t>
+          <t>133174</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>115993</t>
+          <t>133174</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15459</t>
+          <t>15626</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>24501</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10695</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>21821</t>
+          <t>22234</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>14175</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31232</t>
+          <t>34868</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>35,84%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22849</t>
+          <t>24695</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29275</t>
+          <t>31929</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>46762</t>
+          <t>50352</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42430</t>
+          <t>45569</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49760</t>
+          <t>53438</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>69613</t>
+          <t>75047</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60202</t>
+          <t>62413</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78131</t>
+          <t>83106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,43%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>53125</t>
+          <t>56960</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53125</t>
+          <t>56960</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53125</t>
+          <t>56960</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>91434</t>
+          <t>97281</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>91434</t>
+          <t>97281</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>91434</t>
+          <t>97281</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>46641</t>
+          <t>49198</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>58370</t>
+          <t>60420</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>46641</t>
+          <t>49198</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46641</t>
+          <t>49198</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46641</t>
+          <t>49198</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>58370</t>
+          <t>60420</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>58370</t>
+          <t>60420</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58370</t>
+          <t>60420</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>46487</t>
+          <t>49506</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34408</t>
+          <t>37208</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62141</t>
+          <t>65509</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>26205</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>62259</t>
+          <t>66076</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48091</t>
+          <t>51240</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78353</t>
+          <t>84363</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>150434</t>
+          <t>167575</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>134780</t>
+          <t>151572</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>162513</t>
+          <t>179873</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>191864</t>
+          <t>208842</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>183107</t>
+          <t>199207</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>197447</t>
+          <t>214792</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>342299</t>
+          <t>376416</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>326205</t>
+          <t>358129</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>356467</t>
+          <t>391252</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,42%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>196921</t>
+          <t>217081</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>196921</t>
+          <t>217081</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>196921</t>
+          <t>217081</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>207636</t>
+          <t>225412</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>207636</t>
+          <t>225412</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>207636</t>
+          <t>225412</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>404558</t>
+          <t>442492</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>404558</t>
+          <t>442492</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>404558</t>
+          <t>442492</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
